--- a/quiz/updated-drill-questions/DRT2.xlsx
+++ b/quiz/updated-drill-questions/DRT2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_5 QUESTION DATABASE\_1 Access Database\Driller's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\updated-drill-questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D6FDF6-1C4B-4440-8D53-6275803D9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633C7961-B9A1-4C2F-8587-93B87E2BECBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRT2" sheetId="6" r:id="rId1"/>
@@ -1365,7 +1365,7 @@
     <t>DRT2.69</t>
   </si>
   <si>
-    <t>Driller's Day 2 Practice Test</t>
+    <t>Driller's Day 2 Practice Test Questions</t>
   </si>
 </sst>
 </file>
